--- a/research/traditional_assets/database/data/nigeria/nigeria_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_restaurant_dining.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0765</v>
+        <v>-0.0784</v>
       </c>
       <c r="G2">
-        <v>-0.1307420494699646</v>
+        <v>0.08538461538461538</v>
       </c>
       <c r="H2">
-        <v>-0.1307420494699646</v>
+        <v>0.08538461538461538</v>
       </c>
       <c r="I2">
-        <v>-0.3568904593639576</v>
+        <v>-0.03961538461538461</v>
       </c>
       <c r="J2">
-        <v>-0.3568904593639576</v>
+        <v>-0.03961538461538461</v>
       </c>
       <c r="K2">
-        <v>-0.052</v>
+        <v>-0.589</v>
       </c>
       <c r="L2">
-        <v>-0.01837455830388693</v>
+        <v>-0.2265384615384615</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="V2">
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="W2">
-        <v>-0.2407407407407407</v>
+        <v>0.02941176470588236</v>
       </c>
       <c r="X2">
-        <v>0.2474002037075105</v>
-      </c>
-      <c r="Y2">
-        <v>-0.4881409444482512</v>
-      </c>
-      <c r="Z2">
-        <v>2.090103397341212</v>
-      </c>
-      <c r="AA2">
-        <v>-0.7459379615952734</v>
+        <v>0.1921332243486816</v>
       </c>
       <c r="AB2">
-        <v>0.1874355231291222</v>
-      </c>
-      <c r="AC2">
-        <v>-0.9333734847243955</v>
+        <v>0.1734152604571297</v>
       </c>
       <c r="AD2">
-        <v>0.953</v>
+        <v>0.404</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.953</v>
+        <v>0.404</v>
       </c>
       <c r="AG2">
-        <v>0.7529999999999999</v>
+        <v>0.354</v>
       </c>
       <c r="AH2">
-        <v>0.3982448809026327</v>
+        <v>0.1920152091254753</v>
       </c>
       <c r="AI2">
-        <v>0.8982092365692743</v>
+        <v>0.4076690211907165</v>
       </c>
       <c r="AJ2">
-        <v>0.3433652530779754</v>
+        <v>0.1723466407010711</v>
       </c>
       <c r="AK2">
-        <v>0.8745644599303136</v>
+        <v>0.3761955366631243</v>
       </c>
       <c r="AL2">
-        <v>0.159</v>
+        <v>0.175</v>
       </c>
       <c r="AM2">
-        <v>0.133</v>
+        <v>0.175</v>
       </c>
       <c r="AN2">
-        <v>-1.153753026634383</v>
+        <v>1.81981981981982</v>
       </c>
       <c r="AO2">
-        <v>-6.352201257861635</v>
+        <v>-0.5885714285714285</v>
       </c>
       <c r="AP2">
-        <v>-0.9116222760290557</v>
+        <v>1.594594594594595</v>
       </c>
       <c r="AQ2">
-        <v>-7.593984962406014</v>
+        <v>-0.5885714285714285</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +701,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0765</v>
+        <v>-0.0784</v>
       </c>
       <c r="G3">
-        <v>-0.1307420494699646</v>
+        <v>0.08538461538461538</v>
       </c>
       <c r="H3">
-        <v>-0.1307420494699646</v>
+        <v>0.08538461538461538</v>
       </c>
       <c r="I3">
-        <v>-0.3568904593639576</v>
+        <v>-0.03961538461538461</v>
       </c>
       <c r="J3">
-        <v>-0.3568904593639576</v>
+        <v>-0.03961538461538461</v>
       </c>
       <c r="K3">
-        <v>-0.052</v>
+        <v>-0.589</v>
       </c>
       <c r="L3">
-        <v>-0.01837455830388693</v>
+        <v>-0.2265384615384615</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +743,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="V3">
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="W3">
-        <v>-0.2407407407407407</v>
+        <v>0.02941176470588236</v>
       </c>
       <c r="X3">
-        <v>0.2474002037075105</v>
-      </c>
-      <c r="Y3">
-        <v>-0.4881409444482512</v>
-      </c>
-      <c r="Z3">
-        <v>2.090103397341212</v>
-      </c>
-      <c r="AA3">
-        <v>-0.7459379615952734</v>
+        <v>0.1921332243486816</v>
       </c>
       <c r="AB3">
-        <v>0.1874355231291222</v>
-      </c>
-      <c r="AC3">
-        <v>-0.9333734847243955</v>
+        <v>0.1734152604571297</v>
       </c>
       <c r="AD3">
-        <v>0.953</v>
+        <v>0.404</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.953</v>
+        <v>0.404</v>
       </c>
       <c r="AG3">
-        <v>0.7529999999999999</v>
+        <v>0.354</v>
       </c>
       <c r="AH3">
-        <v>0.3982448809026327</v>
+        <v>0.1920152091254753</v>
       </c>
       <c r="AI3">
-        <v>0.8982092365692743</v>
+        <v>0.4076690211907165</v>
       </c>
       <c r="AJ3">
-        <v>0.3433652530779754</v>
+        <v>0.1723466407010711</v>
       </c>
       <c r="AK3">
-        <v>0.8745644599303136</v>
+        <v>0.3761955366631243</v>
       </c>
       <c r="AL3">
-        <v>0.159</v>
+        <v>0.175</v>
       </c>
       <c r="AM3">
-        <v>0.133</v>
+        <v>0.175</v>
       </c>
       <c r="AN3">
-        <v>-1.153753026634383</v>
+        <v>1.81981981981982</v>
       </c>
       <c r="AO3">
-        <v>-6.352201257861635</v>
+        <v>-0.5885714285714285</v>
       </c>
       <c r="AP3">
-        <v>-0.9116222760290557</v>
+        <v>1.594594594594595</v>
       </c>
       <c r="AQ3">
-        <v>-7.593984962406014</v>
+        <v>-0.5885714285714285</v>
       </c>
     </row>
   </sheetData>
